--- a/Data/08 25 CONTROL TRABAJADOR INDEPENDIENTE AGOSTO 2025.xlsx
+++ b/Data/08 25 CONTROL TRABAJADOR INDEPENDIENTE AGOSTO 2025.xlsx
@@ -690,7 +690,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-05-20 13:31:07</t>
+          <t>2026-06-03 11:57:17</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -700,7 +700,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>C:\Users\Dembe\Proyects\Python\AsistenteIMSS\Data\08 MENSAJE TI AGOSTO TOTAL id.pdf</t>
+          <t>C:\Users\Dembe\Proyects\Python\AsistenteIMSS\Data\pdf\ALBERTO FLORES AVILA\Comprobante.pdf</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr"/>

--- a/Data/08 25 CONTROL TRABAJADOR INDEPENDIENTE AGOSTO 2025.xlsx
+++ b/Data/08 25 CONTROL TRABAJADOR INDEPENDIENTE AGOSTO 2025.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH246"/>
+  <dimension ref="A1:AI246"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -602,6 +602,11 @@
       <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>MENSAJE</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>INTENTOS</t>
         </is>
       </c>
     </row>
@@ -690,7 +695,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-06-03 11:57:17</t>
+          <t>2026-06-11 12:10:20</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -720,6 +725,9 @@
         </is>
       </c>
       <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -832,6 +840,7 @@
         </is>
       </c>
       <c r="AH3" t="inlineStr"/>
+      <c r="AI3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -944,6 +953,7 @@
         </is>
       </c>
       <c r="AH4" t="inlineStr"/>
+      <c r="AI4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1042,6 +1052,7 @@
       <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="inlineStr"/>
       <c r="AH5" t="inlineStr"/>
+      <c r="AI5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1140,6 +1151,7 @@
       <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="inlineStr"/>
       <c r="AH6" t="inlineStr"/>
+      <c r="AI6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1238,6 +1250,7 @@
       <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="inlineStr"/>
       <c r="AH7" t="inlineStr"/>
+      <c r="AI7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1340,6 +1353,7 @@
       <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="inlineStr"/>
       <c r="AH8" t="inlineStr"/>
+      <c r="AI8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1438,6 +1452,7 @@
       <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="inlineStr"/>
       <c r="AH9" t="inlineStr"/>
+      <c r="AI9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1536,6 +1551,7 @@
       <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="inlineStr"/>
       <c r="AH10" t="inlineStr"/>
+      <c r="AI10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1634,6 +1650,7 @@
       <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="inlineStr"/>
       <c r="AH11" t="inlineStr"/>
+      <c r="AI11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1720,6 +1737,7 @@
       <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="inlineStr"/>
       <c r="AH12" t="inlineStr"/>
+      <c r="AI12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1806,6 +1824,7 @@
       <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="inlineStr"/>
       <c r="AH13" t="inlineStr"/>
+      <c r="AI13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1888,6 +1907,7 @@
       <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="inlineStr"/>
       <c r="AH14" t="inlineStr"/>
+      <c r="AI14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1974,6 +1994,7 @@
       <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="inlineStr"/>
       <c r="AH15" t="inlineStr"/>
+      <c r="AI15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2062,6 +2083,7 @@
       <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="inlineStr"/>
       <c r="AH16" t="inlineStr"/>
+      <c r="AI16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2148,6 +2170,7 @@
       <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="inlineStr"/>
       <c r="AH17" t="inlineStr"/>
+      <c r="AI17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2230,6 +2253,7 @@
       <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="inlineStr"/>
       <c r="AH18" t="inlineStr"/>
+      <c r="AI18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2316,6 +2340,7 @@
       <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="inlineStr"/>
       <c r="AH19" t="inlineStr"/>
+      <c r="AI19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2398,6 +2423,7 @@
       <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="inlineStr"/>
       <c r="AH20" t="inlineStr"/>
+      <c r="AI20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2480,6 +2506,7 @@
       <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="inlineStr"/>
       <c r="AH21" t="inlineStr"/>
+      <c r="AI21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2570,6 +2597,7 @@
       <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="inlineStr"/>
       <c r="AH22" t="inlineStr"/>
+      <c r="AI22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2652,6 +2680,7 @@
       <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="inlineStr"/>
       <c r="AH23" t="inlineStr"/>
+      <c r="AI23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2734,6 +2763,7 @@
       <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="inlineStr"/>
       <c r="AH24" t="inlineStr"/>
+      <c r="AI24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2822,6 +2852,7 @@
       <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="inlineStr"/>
       <c r="AH25" t="inlineStr"/>
+      <c r="AI25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2906,6 +2937,7 @@
       <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="inlineStr"/>
       <c r="AH26" t="inlineStr"/>
+      <c r="AI26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2992,6 +3024,7 @@
       <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="inlineStr"/>
       <c r="AH27" t="inlineStr"/>
+      <c r="AI27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -3074,6 +3107,7 @@
       <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="inlineStr"/>
       <c r="AH28" t="inlineStr"/>
+      <c r="AI28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -3156,6 +3190,7 @@
       <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="inlineStr"/>
       <c r="AH29" t="inlineStr"/>
+      <c r="AI29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -3238,6 +3273,7 @@
       <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="inlineStr"/>
       <c r="AH30" t="inlineStr"/>
+      <c r="AI30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -3324,6 +3360,7 @@
       <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="inlineStr"/>
       <c r="AH31" t="inlineStr"/>
+      <c r="AI31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -3410,6 +3447,7 @@
       <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="inlineStr"/>
       <c r="AH32" t="inlineStr"/>
+      <c r="AI32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -3496,6 +3534,7 @@
       <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="inlineStr"/>
       <c r="AH33" t="inlineStr"/>
+      <c r="AI33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -3578,6 +3617,7 @@
       <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="inlineStr"/>
       <c r="AH34" t="inlineStr"/>
+      <c r="AI34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -3660,6 +3700,7 @@
       <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="inlineStr"/>
       <c r="AH35" t="inlineStr"/>
+      <c r="AI35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -3746,6 +3787,7 @@
       <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="inlineStr"/>
       <c r="AH36" t="inlineStr"/>
+      <c r="AI36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -3828,6 +3870,7 @@
       <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="inlineStr"/>
       <c r="AH37" t="inlineStr"/>
+      <c r="AI37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -3918,6 +3961,7 @@
       <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="inlineStr"/>
       <c r="AH38" t="inlineStr"/>
+      <c r="AI38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -4000,6 +4044,7 @@
       <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="inlineStr"/>
       <c r="AH39" t="inlineStr"/>
+      <c r="AI39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -4082,6 +4127,7 @@
       <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="inlineStr"/>
       <c r="AH40" t="inlineStr"/>
+      <c r="AI40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -4164,6 +4210,7 @@
       <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="inlineStr"/>
       <c r="AH41" t="inlineStr"/>
+      <c r="AI41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -4250,6 +4297,7 @@
       <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="inlineStr"/>
       <c r="AH42" t="inlineStr"/>
+      <c r="AI42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -4332,6 +4380,7 @@
       <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="inlineStr"/>
       <c r="AH43" t="inlineStr"/>
+      <c r="AI43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -4418,6 +4467,7 @@
       <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="inlineStr"/>
       <c r="AH44" t="inlineStr"/>
+      <c r="AI44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -4502,6 +4552,7 @@
       <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="inlineStr"/>
       <c r="AH45" t="inlineStr"/>
+      <c r="AI45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -4588,6 +4639,7 @@
       <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="inlineStr"/>
       <c r="AH46" t="inlineStr"/>
+      <c r="AI46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -4674,6 +4726,7 @@
       <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="inlineStr"/>
       <c r="AH47" t="inlineStr"/>
+      <c r="AI47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -4756,6 +4809,7 @@
       <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="inlineStr"/>
       <c r="AH48" t="inlineStr"/>
+      <c r="AI48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -4842,6 +4896,7 @@
       <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="inlineStr"/>
       <c r="AH49" t="inlineStr"/>
+      <c r="AI49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -4928,6 +4983,7 @@
       <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="inlineStr"/>
       <c r="AH50" t="inlineStr"/>
+      <c r="AI50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -5016,6 +5072,7 @@
       <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="inlineStr"/>
       <c r="AH51" t="inlineStr"/>
+      <c r="AI51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -5104,6 +5161,7 @@
       <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="inlineStr"/>
       <c r="AH52" t="inlineStr"/>
+      <c r="AI52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -5190,6 +5248,7 @@
       <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="inlineStr"/>
       <c r="AH53" t="inlineStr"/>
+      <c r="AI53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -5272,6 +5331,7 @@
       <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="inlineStr"/>
       <c r="AH54" t="inlineStr"/>
+      <c r="AI54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -5354,6 +5414,7 @@
       <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="inlineStr"/>
       <c r="AH55" t="inlineStr"/>
+      <c r="AI55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -5444,6 +5505,7 @@
       <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="inlineStr"/>
       <c r="AH56" t="inlineStr"/>
+      <c r="AI56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -5530,6 +5592,7 @@
       <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="inlineStr"/>
       <c r="AH57" t="inlineStr"/>
+      <c r="AI57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -5612,6 +5675,7 @@
       <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="inlineStr"/>
       <c r="AH58" t="inlineStr"/>
+      <c r="AI58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -5700,6 +5764,7 @@
       <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="inlineStr"/>
       <c r="AH59" t="inlineStr"/>
+      <c r="AI59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -5782,6 +5847,7 @@
       <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="inlineStr"/>
       <c r="AH60" t="inlineStr"/>
+      <c r="AI60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -5864,6 +5930,7 @@
       <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="inlineStr"/>
       <c r="AH61" t="inlineStr"/>
+      <c r="AI61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -5946,6 +6013,7 @@
       <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="inlineStr"/>
       <c r="AH62" t="inlineStr"/>
+      <c r="AI62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -6028,6 +6096,7 @@
       <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="inlineStr"/>
       <c r="AH63" t="inlineStr"/>
+      <c r="AI63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -6110,6 +6179,7 @@
       <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="inlineStr"/>
       <c r="AH64" t="inlineStr"/>
+      <c r="AI64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -6192,6 +6262,7 @@
       <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="inlineStr"/>
       <c r="AH65" t="inlineStr"/>
+      <c r="AI65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -6274,6 +6345,7 @@
       <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="inlineStr"/>
       <c r="AH66" t="inlineStr"/>
+      <c r="AI66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -6356,6 +6428,7 @@
       <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="inlineStr"/>
       <c r="AH67" t="inlineStr"/>
+      <c r="AI67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -6438,6 +6511,7 @@
       <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="inlineStr"/>
       <c r="AH68" t="inlineStr"/>
+      <c r="AI68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -6524,6 +6598,7 @@
       <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="inlineStr"/>
       <c r="AH69" t="inlineStr"/>
+      <c r="AI69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -6610,6 +6685,7 @@
       <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="inlineStr"/>
       <c r="AH70" t="inlineStr"/>
+      <c r="AI70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -6692,6 +6768,7 @@
       <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="inlineStr"/>
       <c r="AH71" t="inlineStr"/>
+      <c r="AI71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -6782,6 +6859,7 @@
       <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="inlineStr"/>
       <c r="AH72" t="inlineStr"/>
+      <c r="AI72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -6864,6 +6942,7 @@
       <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="inlineStr"/>
       <c r="AH73" t="inlineStr"/>
+      <c r="AI73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -6950,6 +7029,7 @@
       <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="inlineStr"/>
       <c r="AH74" t="inlineStr"/>
+      <c r="AI74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -7032,6 +7112,7 @@
       <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="inlineStr"/>
       <c r="AH75" t="inlineStr"/>
+      <c r="AI75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -7120,6 +7201,7 @@
       <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="inlineStr"/>
       <c r="AH76" t="inlineStr"/>
+      <c r="AI76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -7206,6 +7288,7 @@
       <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="inlineStr"/>
       <c r="AH77" t="inlineStr"/>
+      <c r="AI77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -7288,6 +7371,7 @@
       <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="inlineStr"/>
       <c r="AH78" t="inlineStr"/>
+      <c r="AI78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -7374,6 +7458,7 @@
       <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="inlineStr"/>
       <c r="AH79" t="inlineStr"/>
+      <c r="AI79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -7456,6 +7541,7 @@
       <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="inlineStr"/>
       <c r="AH80" t="inlineStr"/>
+      <c r="AI80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -7538,6 +7624,7 @@
       <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="inlineStr"/>
       <c r="AH81" t="inlineStr"/>
+      <c r="AI81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -7620,6 +7707,7 @@
       <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="inlineStr"/>
       <c r="AH82" t="inlineStr"/>
+      <c r="AI82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -7706,6 +7794,7 @@
       <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="inlineStr"/>
       <c r="AH83" t="inlineStr"/>
+      <c r="AI83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -7788,6 +7877,7 @@
       <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="inlineStr"/>
       <c r="AH84" t="inlineStr"/>
+      <c r="AI84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -7874,6 +7964,7 @@
       <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="inlineStr"/>
       <c r="AH85" t="inlineStr"/>
+      <c r="AI85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -7960,6 +8051,7 @@
       <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="inlineStr"/>
       <c r="AH86" t="inlineStr"/>
+      <c r="AI86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -8042,6 +8134,7 @@
       <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="inlineStr"/>
       <c r="AH87" t="inlineStr"/>
+      <c r="AI87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -8124,6 +8217,7 @@
       <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="inlineStr"/>
       <c r="AH88" t="inlineStr"/>
+      <c r="AI88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -8210,6 +8304,7 @@
       <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="inlineStr"/>
       <c r="AH89" t="inlineStr"/>
+      <c r="AI89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -8292,6 +8387,7 @@
       <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="inlineStr"/>
       <c r="AH90" t="inlineStr"/>
+      <c r="AI90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -8374,6 +8470,7 @@
       <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="inlineStr"/>
       <c r="AH91" t="inlineStr"/>
+      <c r="AI91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -8460,6 +8557,7 @@
       <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="inlineStr"/>
       <c r="AH92" t="inlineStr"/>
+      <c r="AI92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -8542,6 +8640,7 @@
       <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="inlineStr"/>
       <c r="AH93" t="inlineStr"/>
+      <c r="AI93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -8624,6 +8723,7 @@
       <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="inlineStr"/>
       <c r="AH94" t="inlineStr"/>
+      <c r="AI94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -8706,6 +8806,7 @@
       <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="inlineStr"/>
       <c r="AH95" t="inlineStr"/>
+      <c r="AI95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -8792,6 +8893,7 @@
       <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="inlineStr"/>
       <c r="AH96" t="inlineStr"/>
+      <c r="AI96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -8874,6 +8976,7 @@
       <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="inlineStr"/>
       <c r="AH97" t="inlineStr"/>
+      <c r="AI97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -8956,6 +9059,7 @@
       <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="inlineStr"/>
       <c r="AH98" t="inlineStr"/>
+      <c r="AI98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -9038,6 +9142,7 @@
       <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="inlineStr"/>
       <c r="AH99" t="inlineStr"/>
+      <c r="AI99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -9120,6 +9225,7 @@
       <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="inlineStr"/>
       <c r="AH100" t="inlineStr"/>
+      <c r="AI100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -9202,6 +9308,7 @@
       <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="inlineStr"/>
       <c r="AH101" t="inlineStr"/>
+      <c r="AI101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -9288,6 +9395,7 @@
       <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="inlineStr"/>
       <c r="AH102" t="inlineStr"/>
+      <c r="AI102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -9370,6 +9478,7 @@
       <c r="AF103" t="inlineStr"/>
       <c r="AG103" t="inlineStr"/>
       <c r="AH103" t="inlineStr"/>
+      <c r="AI103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -9456,6 +9565,7 @@
       <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="inlineStr"/>
       <c r="AH104" t="inlineStr"/>
+      <c r="AI104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -9544,6 +9654,7 @@
       <c r="AF105" t="inlineStr"/>
       <c r="AG105" t="inlineStr"/>
       <c r="AH105" t="inlineStr"/>
+      <c r="AI105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -9626,6 +9737,7 @@
       <c r="AF106" t="inlineStr"/>
       <c r="AG106" t="inlineStr"/>
       <c r="AH106" t="inlineStr"/>
+      <c r="AI106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -9708,6 +9820,7 @@
       <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="inlineStr"/>
       <c r="AH107" t="inlineStr"/>
+      <c r="AI107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -9794,6 +9907,7 @@
       <c r="AF108" t="inlineStr"/>
       <c r="AG108" t="inlineStr"/>
       <c r="AH108" t="inlineStr"/>
+      <c r="AI108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -9880,6 +9994,7 @@
       <c r="AF109" t="inlineStr"/>
       <c r="AG109" t="inlineStr"/>
       <c r="AH109" t="inlineStr"/>
+      <c r="AI109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -9962,6 +10077,7 @@
       <c r="AF110" t="inlineStr"/>
       <c r="AG110" t="inlineStr"/>
       <c r="AH110" t="inlineStr"/>
+      <c r="AI110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -10044,6 +10160,7 @@
       <c r="AF111" t="inlineStr"/>
       <c r="AG111" t="inlineStr"/>
       <c r="AH111" t="inlineStr"/>
+      <c r="AI111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -10126,6 +10243,7 @@
       <c r="AF112" t="inlineStr"/>
       <c r="AG112" t="inlineStr"/>
       <c r="AH112" t="inlineStr"/>
+      <c r="AI112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -10208,6 +10326,7 @@
       <c r="AF113" t="inlineStr"/>
       <c r="AG113" t="inlineStr"/>
       <c r="AH113" t="inlineStr"/>
+      <c r="AI113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -10294,6 +10413,7 @@
       <c r="AF114" t="inlineStr"/>
       <c r="AG114" t="inlineStr"/>
       <c r="AH114" t="inlineStr"/>
+      <c r="AI114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -10380,6 +10500,7 @@
       <c r="AF115" t="inlineStr"/>
       <c r="AG115" t="inlineStr"/>
       <c r="AH115" t="inlineStr"/>
+      <c r="AI115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -10466,6 +10587,7 @@
       <c r="AF116" t="inlineStr"/>
       <c r="AG116" t="inlineStr"/>
       <c r="AH116" t="inlineStr"/>
+      <c r="AI116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -10548,6 +10670,7 @@
       <c r="AF117" t="inlineStr"/>
       <c r="AG117" t="inlineStr"/>
       <c r="AH117" t="inlineStr"/>
+      <c r="AI117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -10638,6 +10761,7 @@
       <c r="AF118" t="inlineStr"/>
       <c r="AG118" t="inlineStr"/>
       <c r="AH118" t="inlineStr"/>
+      <c r="AI118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -10724,6 +10848,7 @@
       <c r="AF119" t="inlineStr"/>
       <c r="AG119" t="inlineStr"/>
       <c r="AH119" t="inlineStr"/>
+      <c r="AI119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -10810,6 +10935,7 @@
       <c r="AF120" t="inlineStr"/>
       <c r="AG120" t="inlineStr"/>
       <c r="AH120" t="inlineStr"/>
+      <c r="AI120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -10896,6 +11022,7 @@
       <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="inlineStr"/>
       <c r="AH121" t="inlineStr"/>
+      <c r="AI121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -10982,6 +11109,7 @@
       <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="inlineStr"/>
       <c r="AH122" t="inlineStr"/>
+      <c r="AI122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -11064,6 +11192,7 @@
       <c r="AF123" t="inlineStr"/>
       <c r="AG123" t="inlineStr"/>
       <c r="AH123" t="inlineStr"/>
+      <c r="AI123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -11146,6 +11275,7 @@
       <c r="AF124" t="inlineStr"/>
       <c r="AG124" t="inlineStr"/>
       <c r="AH124" t="inlineStr"/>
+      <c r="AI124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -11232,6 +11362,7 @@
       <c r="AF125" t="inlineStr"/>
       <c r="AG125" t="inlineStr"/>
       <c r="AH125" t="inlineStr"/>
+      <c r="AI125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -11318,6 +11449,7 @@
       <c r="AF126" t="inlineStr"/>
       <c r="AG126" t="inlineStr"/>
       <c r="AH126" t="inlineStr"/>
+      <c r="AI126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -11404,6 +11536,7 @@
       <c r="AF127" t="inlineStr"/>
       <c r="AG127" t="inlineStr"/>
       <c r="AH127" t="inlineStr"/>
+      <c r="AI127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -11496,6 +11629,7 @@
       <c r="AF128" t="inlineStr"/>
       <c r="AG128" t="inlineStr"/>
       <c r="AH128" t="inlineStr"/>
+      <c r="AI128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -11578,6 +11712,7 @@
       <c r="AF129" t="inlineStr"/>
       <c r="AG129" t="inlineStr"/>
       <c r="AH129" t="inlineStr"/>
+      <c r="AI129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -11664,6 +11799,7 @@
       <c r="AF130" t="inlineStr"/>
       <c r="AG130" t="inlineStr"/>
       <c r="AH130" t="inlineStr"/>
+      <c r="AI130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -11750,6 +11886,7 @@
       <c r="AF131" t="inlineStr"/>
       <c r="AG131" t="inlineStr"/>
       <c r="AH131" t="inlineStr"/>
+      <c r="AI131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -11832,6 +11969,7 @@
       <c r="AF132" t="inlineStr"/>
       <c r="AG132" t="inlineStr"/>
       <c r="AH132" t="inlineStr"/>
+      <c r="AI132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -11914,6 +12052,7 @@
       <c r="AF133" t="inlineStr"/>
       <c r="AG133" t="inlineStr"/>
       <c r="AH133" t="inlineStr"/>
+      <c r="AI133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -11996,6 +12135,7 @@
       <c r="AF134" t="inlineStr"/>
       <c r="AG134" t="inlineStr"/>
       <c r="AH134" t="inlineStr"/>
+      <c r="AI134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -12078,6 +12218,7 @@
       <c r="AF135" t="inlineStr"/>
       <c r="AG135" t="inlineStr"/>
       <c r="AH135" t="inlineStr"/>
+      <c r="AI135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -12164,6 +12305,7 @@
       <c r="AF136" t="inlineStr"/>
       <c r="AG136" t="inlineStr"/>
       <c r="AH136" t="inlineStr"/>
+      <c r="AI136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -12250,6 +12392,7 @@
       <c r="AF137" t="inlineStr"/>
       <c r="AG137" t="inlineStr"/>
       <c r="AH137" t="inlineStr"/>
+      <c r="AI137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -12336,6 +12479,7 @@
       <c r="AF138" t="inlineStr"/>
       <c r="AG138" t="inlineStr"/>
       <c r="AH138" t="inlineStr"/>
+      <c r="AI138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -12422,6 +12566,7 @@
       <c r="AF139" t="inlineStr"/>
       <c r="AG139" t="inlineStr"/>
       <c r="AH139" t="inlineStr"/>
+      <c r="AI139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -12508,6 +12653,7 @@
       <c r="AF140" t="inlineStr"/>
       <c r="AG140" t="inlineStr"/>
       <c r="AH140" t="inlineStr"/>
+      <c r="AI140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -12590,6 +12736,7 @@
       <c r="AF141" t="inlineStr"/>
       <c r="AG141" t="inlineStr"/>
       <c r="AH141" t="inlineStr"/>
+      <c r="AI141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -12672,6 +12819,7 @@
       <c r="AF142" t="inlineStr"/>
       <c r="AG142" t="inlineStr"/>
       <c r="AH142" t="inlineStr"/>
+      <c r="AI142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -12758,6 +12906,7 @@
       <c r="AF143" t="inlineStr"/>
       <c r="AG143" t="inlineStr"/>
       <c r="AH143" t="inlineStr"/>
+      <c r="AI143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -12844,6 +12993,7 @@
       <c r="AF144" t="inlineStr"/>
       <c r="AG144" t="inlineStr"/>
       <c r="AH144" t="inlineStr"/>
+      <c r="AI144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -12930,6 +13080,7 @@
       <c r="AF145" t="inlineStr"/>
       <c r="AG145" t="inlineStr"/>
       <c r="AH145" t="inlineStr"/>
+      <c r="AI145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -13012,6 +13163,7 @@
       <c r="AF146" t="inlineStr"/>
       <c r="AG146" t="inlineStr"/>
       <c r="AH146" t="inlineStr"/>
+      <c r="AI146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -13094,6 +13246,7 @@
       <c r="AF147" t="inlineStr"/>
       <c r="AG147" t="inlineStr"/>
       <c r="AH147" t="inlineStr"/>
+      <c r="AI147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -13180,6 +13333,7 @@
       <c r="AF148" t="inlineStr"/>
       <c r="AG148" t="inlineStr"/>
       <c r="AH148" t="inlineStr"/>
+      <c r="AI148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -13262,6 +13416,7 @@
       <c r="AF149" t="inlineStr"/>
       <c r="AG149" t="inlineStr"/>
       <c r="AH149" t="inlineStr"/>
+      <c r="AI149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -13344,6 +13499,7 @@
       <c r="AF150" t="inlineStr"/>
       <c r="AG150" t="inlineStr"/>
       <c r="AH150" t="inlineStr"/>
+      <c r="AI150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -13426,6 +13582,7 @@
       <c r="AF151" t="inlineStr"/>
       <c r="AG151" t="inlineStr"/>
       <c r="AH151" t="inlineStr"/>
+      <c r="AI151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -13514,6 +13671,7 @@
       <c r="AF152" t="inlineStr"/>
       <c r="AG152" t="inlineStr"/>
       <c r="AH152" t="inlineStr"/>
+      <c r="AI152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -13596,6 +13754,7 @@
       <c r="AF153" t="inlineStr"/>
       <c r="AG153" t="inlineStr"/>
       <c r="AH153" t="inlineStr"/>
+      <c r="AI153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -13678,6 +13837,7 @@
       <c r="AF154" t="inlineStr"/>
       <c r="AG154" t="inlineStr"/>
       <c r="AH154" t="inlineStr"/>
+      <c r="AI154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -13760,6 +13920,7 @@
       <c r="AF155" t="inlineStr"/>
       <c r="AG155" t="inlineStr"/>
       <c r="AH155" t="inlineStr"/>
+      <c r="AI155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -13846,6 +14007,7 @@
       <c r="AF156" t="inlineStr"/>
       <c r="AG156" t="inlineStr"/>
       <c r="AH156" t="inlineStr"/>
+      <c r="AI156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -13928,6 +14090,7 @@
       <c r="AF157" t="inlineStr"/>
       <c r="AG157" t="inlineStr"/>
       <c r="AH157" t="inlineStr"/>
+      <c r="AI157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -14010,6 +14173,7 @@
       <c r="AF158" t="inlineStr"/>
       <c r="AG158" t="inlineStr"/>
       <c r="AH158" t="inlineStr"/>
+      <c r="AI158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -14092,6 +14256,7 @@
       <c r="AF159" t="inlineStr"/>
       <c r="AG159" t="inlineStr"/>
       <c r="AH159" t="inlineStr"/>
+      <c r="AI159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -14182,6 +14347,7 @@
       <c r="AF160" t="inlineStr"/>
       <c r="AG160" t="inlineStr"/>
       <c r="AH160" t="inlineStr"/>
+      <c r="AI160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -14268,6 +14434,7 @@
       <c r="AF161" t="inlineStr"/>
       <c r="AG161" t="inlineStr"/>
       <c r="AH161" t="inlineStr"/>
+      <c r="AI161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -14356,6 +14523,7 @@
       <c r="AF162" t="inlineStr"/>
       <c r="AG162" t="inlineStr"/>
       <c r="AH162" t="inlineStr"/>
+      <c r="AI162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -14446,6 +14614,7 @@
       <c r="AF163" t="inlineStr"/>
       <c r="AG163" t="inlineStr"/>
       <c r="AH163" t="inlineStr"/>
+      <c r="AI163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -14528,6 +14697,7 @@
       <c r="AF164" t="inlineStr"/>
       <c r="AG164" t="inlineStr"/>
       <c r="AH164" t="inlineStr"/>
+      <c r="AI164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -14610,6 +14780,7 @@
       <c r="AF165" t="inlineStr"/>
       <c r="AG165" t="inlineStr"/>
       <c r="AH165" t="inlineStr"/>
+      <c r="AI165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -14696,6 +14867,7 @@
       <c r="AF166" t="inlineStr"/>
       <c r="AG166" t="inlineStr"/>
       <c r="AH166" t="inlineStr"/>
+      <c r="AI166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -14778,6 +14950,7 @@
       <c r="AF167" t="inlineStr"/>
       <c r="AG167" t="inlineStr"/>
       <c r="AH167" t="inlineStr"/>
+      <c r="AI167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -14860,6 +15033,7 @@
       <c r="AF168" t="inlineStr"/>
       <c r="AG168" t="inlineStr"/>
       <c r="AH168" t="inlineStr"/>
+      <c r="AI168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -14946,6 +15120,7 @@
       <c r="AF169" t="inlineStr"/>
       <c r="AG169" t="inlineStr"/>
       <c r="AH169" t="inlineStr"/>
+      <c r="AI169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -15032,6 +15207,7 @@
       <c r="AF170" t="inlineStr"/>
       <c r="AG170" t="inlineStr"/>
       <c r="AH170" t="inlineStr"/>
+      <c r="AI170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -15114,6 +15290,7 @@
       <c r="AF171" t="inlineStr"/>
       <c r="AG171" t="inlineStr"/>
       <c r="AH171" t="inlineStr"/>
+      <c r="AI171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -15200,6 +15377,7 @@
       <c r="AF172" t="inlineStr"/>
       <c r="AG172" t="inlineStr"/>
       <c r="AH172" t="inlineStr"/>
+      <c r="AI172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -15286,6 +15464,7 @@
       <c r="AF173" t="inlineStr"/>
       <c r="AG173" t="inlineStr"/>
       <c r="AH173" t="inlineStr"/>
+      <c r="AI173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -15368,6 +15547,7 @@
       <c r="AF174" t="inlineStr"/>
       <c r="AG174" t="inlineStr"/>
       <c r="AH174" t="inlineStr"/>
+      <c r="AI174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -15450,6 +15630,7 @@
       <c r="AF175" t="inlineStr"/>
       <c r="AG175" t="inlineStr"/>
       <c r="AH175" t="inlineStr"/>
+      <c r="AI175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -15536,6 +15717,7 @@
       <c r="AF176" t="inlineStr"/>
       <c r="AG176" t="inlineStr"/>
       <c r="AH176" t="inlineStr"/>
+      <c r="AI176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -15622,6 +15804,7 @@
       <c r="AF177" t="inlineStr"/>
       <c r="AG177" t="inlineStr"/>
       <c r="AH177" t="inlineStr"/>
+      <c r="AI177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -15704,6 +15887,7 @@
       <c r="AF178" t="inlineStr"/>
       <c r="AG178" t="inlineStr"/>
       <c r="AH178" t="inlineStr"/>
+      <c r="AI178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -15790,6 +15974,7 @@
       <c r="AF179" t="inlineStr"/>
       <c r="AG179" t="inlineStr"/>
       <c r="AH179" t="inlineStr"/>
+      <c r="AI179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -15874,6 +16059,7 @@
       <c r="AF180" t="inlineStr"/>
       <c r="AG180" t="inlineStr"/>
       <c r="AH180" t="inlineStr"/>
+      <c r="AI180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -15956,6 +16142,7 @@
       <c r="AF181" t="inlineStr"/>
       <c r="AG181" t="inlineStr"/>
       <c r="AH181" t="inlineStr"/>
+      <c r="AI181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -16038,6 +16225,7 @@
       <c r="AF182" t="inlineStr"/>
       <c r="AG182" t="inlineStr"/>
       <c r="AH182" t="inlineStr"/>
+      <c r="AI182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -16120,6 +16308,7 @@
       <c r="AF183" t="inlineStr"/>
       <c r="AG183" t="inlineStr"/>
       <c r="AH183" t="inlineStr"/>
+      <c r="AI183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -16202,6 +16391,7 @@
       <c r="AF184" t="inlineStr"/>
       <c r="AG184" t="inlineStr"/>
       <c r="AH184" t="inlineStr"/>
+      <c r="AI184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -16284,6 +16474,7 @@
       <c r="AF185" t="inlineStr"/>
       <c r="AG185" t="inlineStr"/>
       <c r="AH185" t="inlineStr"/>
+      <c r="AI185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -16372,6 +16563,7 @@
       <c r="AF186" t="inlineStr"/>
       <c r="AG186" t="inlineStr"/>
       <c r="AH186" t="inlineStr"/>
+      <c r="AI186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -16462,6 +16654,7 @@
       <c r="AF187" t="inlineStr"/>
       <c r="AG187" t="inlineStr"/>
       <c r="AH187" t="inlineStr"/>
+      <c r="AI187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -16544,6 +16737,7 @@
       <c r="AF188" t="inlineStr"/>
       <c r="AG188" t="inlineStr"/>
       <c r="AH188" t="inlineStr"/>
+      <c r="AI188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -16626,6 +16820,7 @@
       <c r="AF189" t="inlineStr"/>
       <c r="AG189" t="inlineStr"/>
       <c r="AH189" t="inlineStr"/>
+      <c r="AI189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -16710,6 +16905,7 @@
       <c r="AF190" t="inlineStr"/>
       <c r="AG190" t="inlineStr"/>
       <c r="AH190" t="inlineStr"/>
+      <c r="AI190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -16792,6 +16988,7 @@
       <c r="AF191" t="inlineStr"/>
       <c r="AG191" t="inlineStr"/>
       <c r="AH191" t="inlineStr"/>
+      <c r="AI191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -16878,6 +17075,7 @@
       <c r="AF192" t="inlineStr"/>
       <c r="AG192" t="inlineStr"/>
       <c r="AH192" t="inlineStr"/>
+      <c r="AI192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -16960,6 +17158,7 @@
       <c r="AF193" t="inlineStr"/>
       <c r="AG193" t="inlineStr"/>
       <c r="AH193" t="inlineStr"/>
+      <c r="AI193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -17042,6 +17241,7 @@
       <c r="AF194" t="inlineStr"/>
       <c r="AG194" t="inlineStr"/>
       <c r="AH194" t="inlineStr"/>
+      <c r="AI194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -17128,6 +17328,7 @@
       <c r="AF195" t="inlineStr"/>
       <c r="AG195" t="inlineStr"/>
       <c r="AH195" t="inlineStr"/>
+      <c r="AI195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -17210,6 +17411,7 @@
       <c r="AF196" t="inlineStr"/>
       <c r="AG196" t="inlineStr"/>
       <c r="AH196" t="inlineStr"/>
+      <c r="AI196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -17292,6 +17494,7 @@
       <c r="AF197" t="inlineStr"/>
       <c r="AG197" t="inlineStr"/>
       <c r="AH197" t="inlineStr"/>
+      <c r="AI197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -17374,6 +17577,7 @@
       <c r="AF198" t="inlineStr"/>
       <c r="AG198" t="inlineStr"/>
       <c r="AH198" t="inlineStr"/>
+      <c r="AI198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -17456,6 +17660,7 @@
       <c r="AF199" t="inlineStr"/>
       <c r="AG199" t="inlineStr"/>
       <c r="AH199" t="inlineStr"/>
+      <c r="AI199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -17538,6 +17743,7 @@
       <c r="AF200" t="inlineStr"/>
       <c r="AG200" t="inlineStr"/>
       <c r="AH200" t="inlineStr"/>
+      <c r="AI200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -17622,6 +17828,7 @@
       <c r="AF201" t="inlineStr"/>
       <c r="AG201" t="inlineStr"/>
       <c r="AH201" t="inlineStr"/>
+      <c r="AI201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -17704,6 +17911,7 @@
       <c r="AF202" t="inlineStr"/>
       <c r="AG202" t="inlineStr"/>
       <c r="AH202" t="inlineStr"/>
+      <c r="AI202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -17786,6 +17994,7 @@
       <c r="AF203" t="inlineStr"/>
       <c r="AG203" t="inlineStr"/>
       <c r="AH203" t="inlineStr"/>
+      <c r="AI203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -17872,6 +18081,7 @@
       <c r="AF204" t="inlineStr"/>
       <c r="AG204" t="inlineStr"/>
       <c r="AH204" t="inlineStr"/>
+      <c r="AI204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -17954,6 +18164,7 @@
       <c r="AF205" t="inlineStr"/>
       <c r="AG205" t="inlineStr"/>
       <c r="AH205" t="inlineStr"/>
+      <c r="AI205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -18042,6 +18253,7 @@
       <c r="AF206" t="inlineStr"/>
       <c r="AG206" t="inlineStr"/>
       <c r="AH206" t="inlineStr"/>
+      <c r="AI206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -18124,6 +18336,7 @@
       <c r="AF207" t="inlineStr"/>
       <c r="AG207" t="inlineStr"/>
       <c r="AH207" t="inlineStr"/>
+      <c r="AI207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -18206,6 +18419,7 @@
       <c r="AF208" t="inlineStr"/>
       <c r="AG208" t="inlineStr"/>
       <c r="AH208" t="inlineStr"/>
+      <c r="AI208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -18288,6 +18502,7 @@
       <c r="AF209" t="inlineStr"/>
       <c r="AG209" t="inlineStr"/>
       <c r="AH209" t="inlineStr"/>
+      <c r="AI209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -18370,6 +18585,7 @@
       <c r="AF210" t="inlineStr"/>
       <c r="AG210" t="inlineStr"/>
       <c r="AH210" t="inlineStr"/>
+      <c r="AI210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -18456,6 +18672,7 @@
       <c r="AF211" t="inlineStr"/>
       <c r="AG211" t="inlineStr"/>
       <c r="AH211" t="inlineStr"/>
+      <c r="AI211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -18542,6 +18759,7 @@
       <c r="AF212" t="inlineStr"/>
       <c r="AG212" t="inlineStr"/>
       <c r="AH212" t="inlineStr"/>
+      <c r="AI212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -18624,6 +18842,7 @@
       <c r="AF213" t="inlineStr"/>
       <c r="AG213" t="inlineStr"/>
       <c r="AH213" t="inlineStr"/>
+      <c r="AI213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -18710,6 +18929,7 @@
       <c r="AF214" t="inlineStr"/>
       <c r="AG214" t="inlineStr"/>
       <c r="AH214" t="inlineStr"/>
+      <c r="AI214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -18800,6 +19020,7 @@
       <c r="AF215" t="inlineStr"/>
       <c r="AG215" t="inlineStr"/>
       <c r="AH215" t="inlineStr"/>
+      <c r="AI215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -18886,6 +19107,7 @@
       <c r="AF216" t="inlineStr"/>
       <c r="AG216" t="inlineStr"/>
       <c r="AH216" t="inlineStr"/>
+      <c r="AI216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -18972,6 +19194,7 @@
       <c r="AF217" t="inlineStr"/>
       <c r="AG217" t="inlineStr"/>
       <c r="AH217" t="inlineStr"/>
+      <c r="AI217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -19066,6 +19289,7 @@
       <c r="AF218" t="inlineStr"/>
       <c r="AG218" t="inlineStr"/>
       <c r="AH218" t="inlineStr"/>
+      <c r="AI218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -19152,6 +19376,7 @@
       <c r="AF219" t="inlineStr"/>
       <c r="AG219" t="inlineStr"/>
       <c r="AH219" t="inlineStr"/>
+      <c r="AI219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -19238,6 +19463,7 @@
       <c r="AF220" t="inlineStr"/>
       <c r="AG220" t="inlineStr"/>
       <c r="AH220" t="inlineStr"/>
+      <c r="AI220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -19320,6 +19546,7 @@
       <c r="AF221" t="inlineStr"/>
       <c r="AG221" t="inlineStr"/>
       <c r="AH221" t="inlineStr"/>
+      <c r="AI221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -19402,6 +19629,7 @@
       <c r="AF222" t="inlineStr"/>
       <c r="AG222" t="inlineStr"/>
       <c r="AH222" t="inlineStr"/>
+      <c r="AI222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -19484,6 +19712,7 @@
       <c r="AF223" t="inlineStr"/>
       <c r="AG223" t="inlineStr"/>
       <c r="AH223" t="inlineStr"/>
+      <c r="AI223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -19570,6 +19799,7 @@
       <c r="AF224" t="inlineStr"/>
       <c r="AG224" t="inlineStr"/>
       <c r="AH224" t="inlineStr"/>
+      <c r="AI224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -19652,6 +19882,7 @@
       <c r="AF225" t="inlineStr"/>
       <c r="AG225" t="inlineStr"/>
       <c r="AH225" t="inlineStr"/>
+      <c r="AI225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -19742,6 +19973,7 @@
         </is>
       </c>
       <c r="AH226" t="inlineStr"/>
+      <c r="AI226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -19836,6 +20068,7 @@
         </is>
       </c>
       <c r="AH227" t="inlineStr"/>
+      <c r="AI227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -19918,6 +20151,7 @@
       <c r="AF228" t="inlineStr"/>
       <c r="AG228" t="inlineStr"/>
       <c r="AH228" t="inlineStr"/>
+      <c r="AI228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -19994,6 +20228,7 @@
       <c r="AF229" t="inlineStr"/>
       <c r="AG229" t="inlineStr"/>
       <c r="AH229" t="inlineStr"/>
+      <c r="AI229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -20070,6 +20305,7 @@
       <c r="AF230" t="inlineStr"/>
       <c r="AG230" t="inlineStr"/>
       <c r="AH230" t="inlineStr"/>
+      <c r="AI230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -20146,6 +20382,7 @@
       <c r="AF231" t="inlineStr"/>
       <c r="AG231" t="inlineStr"/>
       <c r="AH231" t="inlineStr"/>
+      <c r="AI231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -20226,6 +20463,7 @@
       <c r="AF232" t="inlineStr"/>
       <c r="AG232" t="inlineStr"/>
       <c r="AH232" t="inlineStr"/>
+      <c r="AI232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -20302,6 +20540,7 @@
       <c r="AF233" t="inlineStr"/>
       <c r="AG233" t="inlineStr"/>
       <c r="AH233" t="inlineStr"/>
+      <c r="AI233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -20378,6 +20617,7 @@
       <c r="AF234" t="inlineStr"/>
       <c r="AG234" t="inlineStr"/>
       <c r="AH234" t="inlineStr"/>
+      <c r="AI234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -20462,6 +20702,7 @@
         </is>
       </c>
       <c r="AH235" t="inlineStr"/>
+      <c r="AI235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -20542,6 +20783,7 @@
       <c r="AF236" t="inlineStr"/>
       <c r="AG236" t="inlineStr"/>
       <c r="AH236" t="inlineStr"/>
+      <c r="AI236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -20622,6 +20864,7 @@
       <c r="AF237" t="inlineStr"/>
       <c r="AG237" t="inlineStr"/>
       <c r="AH237" t="inlineStr"/>
+      <c r="AI237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -20698,6 +20941,7 @@
       <c r="AF238" t="inlineStr"/>
       <c r="AG238" t="inlineStr"/>
       <c r="AH238" t="inlineStr"/>
+      <c r="AI238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -20774,6 +21018,7 @@
       <c r="AF239" t="inlineStr"/>
       <c r="AG239" t="inlineStr"/>
       <c r="AH239" t="inlineStr"/>
+      <c r="AI239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -20850,6 +21095,7 @@
       <c r="AF240" t="inlineStr"/>
       <c r="AG240" t="inlineStr"/>
       <c r="AH240" t="inlineStr"/>
+      <c r="AI240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -20894,6 +21140,7 @@
       <c r="AF241" t="inlineStr"/>
       <c r="AG241" t="inlineStr"/>
       <c r="AH241" t="inlineStr"/>
+      <c r="AI241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -20938,6 +21185,7 @@
       <c r="AF242" t="inlineStr"/>
       <c r="AG242" t="inlineStr"/>
       <c r="AH242" t="inlineStr"/>
+      <c r="AI242" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr"/>
@@ -20974,6 +21222,7 @@
       <c r="AF243" t="inlineStr"/>
       <c r="AG243" t="inlineStr"/>
       <c r="AH243" t="inlineStr"/>
+      <c r="AI243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr"/>
@@ -21010,6 +21259,7 @@
       <c r="AF244" t="inlineStr"/>
       <c r="AG244" t="inlineStr"/>
       <c r="AH244" t="inlineStr"/>
+      <c r="AI244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr"/>
@@ -21050,6 +21300,7 @@
       <c r="AF245" t="inlineStr"/>
       <c r="AG245" t="inlineStr"/>
       <c r="AH245" t="inlineStr"/>
+      <c r="AI245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr"/>
@@ -21114,6 +21365,7 @@
       <c r="AF246" t="inlineStr"/>
       <c r="AG246" t="inlineStr"/>
       <c r="AH246" t="inlineStr"/>
+      <c r="AI246" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Data/08 25 CONTROL TRABAJADOR INDEPENDIENTE AGOSTO 2025.xlsx
+++ b/Data/08 25 CONTROL TRABAJADOR INDEPENDIENTE AGOSTO 2025.xlsx
@@ -695,7 +695,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-06-11 12:10:20</t>
+          <t>2026-07-21 14:05:09</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -705,7 +705,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>C:\Users\Dembe\Proyects\Python\AsistenteIMSS\Data\pdf\ALBERTO FLORES AVILA\Comprobante.pdf</t>
+          <t>C:\Users\sofia\Proyects\IMSS\prueba_imss\prueba_indep\ALBERTO FLORES AVILA\Comprobante (1).pdf</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr"/>
@@ -721,7 +721,7 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>C:/Users/Dembe/Proyects/Python/AsistenteIMSS/Data/pdf</t>
+          <t>C:/Users/sofia/Proyects/IMSS/prueba_imss/prueba_indep</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr"/>
@@ -810,7 +810,7 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-05-17 22:46:41</t>
+          <t>2026-07-21 14:07:03</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>C:\Users\Dembe\Proyects\Python\AsistenteIMSS\Data\pdf\ALDO JOSUE COVA GONZALEZ\Comprobante.pdf</t>
+          <t>C:\Users\sofia\Proyects\IMSS\prueba_imss\prueba_indep\ALDO JOSUE COVA GONZALEZ\Comprobante.pdf</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr"/>
@@ -836,7 +836,7 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>C:/Users/Dembe/Proyects/Python/AsistenteIMSS/Data/pdf</t>
+          <t>C:/Users/sofia/Proyects/IMSS/prueba_imss/prueba_indep</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr"/>
